--- a/summary/test_data_after_stand_summary.xlsx
+++ b/summary/test_data_after_stand_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.9066914829696593</v>
+        <v>-3.51372275852201</v>
       </c>
       <c r="C3" t="n">
-        <v>4.618549076703626</v>
+        <v>3.54378318206067</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06992160488277568</v>
+        <v>-0.06209065808206438</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1120310005163765</v>
+        <v>0.07250432859245991</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4966520103192048</v>
+        <v>0.9705138559104469</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2466632193541075</v>
+        <v>0.9418971445141637</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.5707501337786359</v>
+        <v>-0.8068408258386879</v>
       </c>
       <c r="C4" t="n">
-        <v>6.569360539406416</v>
+        <v>1.919017976538475</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.01905897091500782</v>
+        <v>-0.03123400933166015</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5707501337786359</v>
+        <v>-0.8068408258386879</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9796995204231731</v>
+        <v>0.9944594830576402</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9598111503173954</v>
+        <v>0.988949663443269</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.9730181828073765</v>
+        <v>-1.4141397865663</v>
       </c>
       <c r="C5" t="n">
-        <v>7.821962708549097</v>
+        <v>1.359755117188353</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.01038959857772796</v>
+        <v>-0.003194400053604423</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2053764591228963</v>
+        <v>0.5453160443695331</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9984981692209985</v>
+        <v>0.9938407378181153</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9969985939376858</v>
+        <v>0.9877194121468559</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.2886528311122454</v>
+        <v>-0.3553424078009089</v>
       </c>
       <c r="C6" t="n">
-        <v>9.174090490226712</v>
+        <v>3.619397294573782</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03741666156968608</v>
+        <v>0.02774242919187456</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2886528311122454</v>
+        <v>-0.3553424078009089</v>
       </c>
       <c r="F6" t="n">
-        <v>1.095710461971119</v>
+        <v>1.03650473134005</v>
       </c>
       <c r="G6" t="n">
-        <v>1.200581416472964</v>
+        <v>1.074342058090309</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-1.28417561989079</v>
+        <v>-3.047600483023416</v>
       </c>
       <c r="C7" t="n">
-        <v>3.560570582024979</v>
+        <v>1.090248548991072</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0301673758519683</v>
+        <v>-0.02499996940429135</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2427815764883351</v>
+        <v>0.2616942802953399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9901197039173142</v>
+        <v>1.017019427294358</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9803370280853099</v>
+        <v>1.034328515494143</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +605,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2.411166932760057</v>
+        <v>-5.894038092795351</v>
       </c>
       <c r="C8" t="n">
-        <v>9.206530586956751</v>
+        <v>1.55908504243069</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.02742755395625089</v>
+        <v>-0.03445878275956157</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1583141065617825</v>
+        <v>0.1275926859917272</v>
       </c>
       <c r="F8" t="n">
-        <v>1.011487541017325</v>
+        <v>1.06363056586247</v>
       </c>
       <c r="G8" t="n">
-        <v>1.023107045633274</v>
+        <v>1.131309980636918</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.955275729745824</v>
+        <v>-3.142498956705619</v>
       </c>
       <c r="C9" t="n">
-        <v>10.17549263972948</v>
+        <v>4.814531495952832</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.015764046265467</v>
+        <v>-0.02689889296058504</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2163942569882719</v>
+        <v>-0.07480144481180019</v>
       </c>
       <c r="F9" t="n">
-        <v>1.030302331509694</v>
+        <v>1.033150066875349</v>
       </c>
       <c r="G9" t="n">
-        <v>1.06152289431431</v>
+        <v>1.067399060684537</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +655,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.7951632272572445</v>
+        <v>-0.8701173641387884</v>
       </c>
       <c r="C10" t="n">
-        <v>3.471770713046549</v>
+        <v>1.417101304379369</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.04817987054938506</v>
+        <v>-0.02127073533022548</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7951632272572445</v>
+        <v>-0.8701173641387884</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9638646890224931</v>
+        <v>0.9906482208258371</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9290351387444274</v>
+        <v>0.9813838974253967</v>
       </c>
     </row>
     <row r="11">
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1202417237346725</v>
+        <v>-0.1336023189084742</v>
       </c>
       <c r="C11" t="n">
-        <v>21.76986765378667</v>
+        <v>9.196811486322643</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0473393692266246</v>
+        <v>-0.06082564021632841</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1202417237346725</v>
+        <v>-0.1336023189084742</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9061199048522486</v>
+        <v>0.7457918627386499</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8210532819694479</v>
+        <v>0.5562055025271853</v>
       </c>
     </row>
     <row r="12">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-2.110152042935081</v>
+        <v>-3.773369383838025</v>
       </c>
       <c r="C12" t="n">
-        <v>6.814265409350353</v>
+        <v>3.804747536638441</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.05600181748646695</v>
+        <v>-0.04208946648837993</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1588875615800101</v>
+        <v>-0.002960281451987794</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9243589089290198</v>
+        <v>0.9481633607835332</v>
       </c>
       <c r="G12" t="n">
-        <v>0.854439392516448</v>
+        <v>0.8990137587323246</v>
       </c>
     </row>
     <row r="13">
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2410610357992968</v>
+        <v>-0.2429231735496986</v>
       </c>
       <c r="C14" t="n">
-        <v>8.138679732461972</v>
+        <v>6.515952899906281</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03175437646417841</v>
+        <v>0.03231738131833545</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2410610357992968</v>
+        <v>-0.2429231735496986</v>
       </c>
       <c r="F14" t="n">
-        <v>1.057131881535158</v>
+        <v>1.059175396114358</v>
       </c>
       <c r="G14" t="n">
-        <v>1.117527814958064</v>
+        <v>1.121852519734007</v>
       </c>
     </row>
     <row r="15">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-4.751486354069578</v>
+        <v>-7.975078122202384</v>
       </c>
       <c r="C18" t="n">
-        <v>4.32857919166548</v>
+        <v>4.336071900852138</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.01852552642632109</v>
+        <v>-0.0189434437639029</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2114535812020489</v>
+        <v>-0.2076072719753528</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9464682236086467</v>
+        <v>0.9764078540158971</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8958020983009072</v>
+        <v>0.9533722973839296</v>
       </c>
     </row>
     <row r="19">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-2.165022821016314</v>
+        <v>-3.158172338244525</v>
       </c>
       <c r="C19" t="n">
-        <v>5.220335400207559</v>
+        <v>-2.304982300166768</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.08161613523697217</v>
+        <v>-2.79308723637513</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3186832657103453</v>
+        <v>-2.813758749898229</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9286439129881946</v>
+        <v>0.1224726172068784</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8623795171300255</v>
+        <v>0.01499954196550256</v>
       </c>
     </row>
     <row r="20">
@@ -908,19 +908,19 @@
         <v>-0.9512264882332893</v>
       </c>
       <c r="C20" t="n">
-        <v>5.255659200350409</v>
+        <v>1.546172798104521</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.04933494198260809</v>
+        <v>-0.3635634864496854</v>
       </c>
       <c r="E20" t="n">
         <v>-0.9512264882332893</v>
       </c>
       <c r="F20" t="n">
-        <v>1.004616186167258</v>
+        <v>0.6126876980697885</v>
       </c>
       <c r="G20" t="n">
-        <v>1.009253681509247</v>
+        <v>0.3753862153660563</v>
       </c>
     </row>
     <row r="21">
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.7521758378613592</v>
+        <v>-0.9467014684878265</v>
       </c>
       <c r="C23" t="n">
-        <v>10.61292408399217</v>
+        <v>1.851141160926364</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.008537738435568897</v>
+        <v>-0.005813519417281798</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7521758378613592</v>
+        <v>-0.9467014684878265</v>
       </c>
       <c r="F23" t="n">
-        <v>1.019545886916882</v>
+        <v>0.9975144226316524</v>
       </c>
       <c r="G23" t="n">
-        <v>1.039473815529131</v>
+        <v>0.9950350233581589</v>
       </c>
     </row>
     <row r="24">
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.704483250333654</v>
+        <v>-1.072916474962699</v>
       </c>
       <c r="C24" t="n">
-        <v>10.49833506261706</v>
+        <v>1.999467862252639</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02496687970768756</v>
+        <v>0.02274895877874982</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2817353894675895</v>
+        <v>0.4920665308869768</v>
       </c>
       <c r="F24" t="n">
-        <v>1.040010529574788</v>
+        <v>1.002277710386582</v>
       </c>
       <c r="G24" t="n">
-        <v>1.081621901626432</v>
+        <v>1.004560608737769</v>
       </c>
     </row>
     <row r="25">
@@ -1030,22 +1030,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3593249004055313</v>
+        <v>-0.4042442108783149</v>
       </c>
       <c r="C25" t="n">
-        <v>16.20417077385836</v>
+        <v>3.603730653062192</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03746767064344926</v>
+        <v>0.068843772296505</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3593249004055313</v>
+        <v>-0.4042442108783149</v>
       </c>
       <c r="F25" t="n">
-        <v>1.100322926598291</v>
+        <v>1.050573391074073</v>
       </c>
       <c r="G25" t="n">
-        <v>1.210710542797828</v>
+        <v>1.103704450032877</v>
       </c>
     </row>
     <row r="26">
@@ -1055,22 +1055,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1163392861482226</v>
+        <v>-0.1285214274886148</v>
       </c>
       <c r="C26" t="n">
-        <v>12.16729446224587</v>
+        <v>8.705045196618768</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05511288839996325</v>
+        <v>-0.05846576540103778</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1163392861482226</v>
+        <v>-0.1285214274886148</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6895159081135821</v>
+        <v>0.7410126719471999</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4754321875416978</v>
+        <v>0.5490997799863285</v>
       </c>
     </row>
     <row r="27">
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2702083542015609</v>
+        <v>-0.2927694190084836</v>
       </c>
       <c r="C27" t="n">
-        <v>10.063795809214</v>
+        <v>4.239762916060005</v>
       </c>
       <c r="D27" t="n">
-        <v>0.03594419232069218</v>
+        <v>0.05782549382688938</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2702083542015609</v>
+        <v>-0.2927694190084836</v>
       </c>
       <c r="F27" t="n">
-        <v>1.01563459300344</v>
+        <v>1.079150320875313</v>
       </c>
       <c r="G27" t="n">
-        <v>1.031513626505263</v>
+        <v>1.16456541504529</v>
       </c>
     </row>
     <row r="28">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.06869174753820707</v>
+        <v>-0.06939258050999438</v>
       </c>
       <c r="C28" t="n">
-        <v>19.84986861110774</v>
+        <v>15.17652734628317</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.02526068507011768</v>
+        <v>-0.01400732729409562</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.06869174753820707</v>
+        <v>-0.06939258050999438</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7591871217092994</v>
+        <v>0.8661314924819761</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5763650857692505</v>
+        <v>0.7501837622690554</v>
       </c>
     </row>
     <row r="29">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.08768781151769862</v>
+        <v>-0.1904814736846831</v>
       </c>
       <c r="C29" t="n">
-        <v>34.18974756614443</v>
+        <v>7.757422084593538</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02959731964369525</v>
+        <v>0.002139563366975658</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.08768781151769862</v>
+        <v>-0.1904814736846831</v>
       </c>
       <c r="F29" t="n">
-        <v>1.271908553535858</v>
+        <v>1.02369480634146</v>
       </c>
       <c r="G29" t="n">
-        <v>1.617751368557678</v>
+        <v>1.04795105653048</v>
       </c>
     </row>
     <row r="30">
@@ -1246,6 +1246,181 @@
       </c>
       <c r="G33" t="n">
         <v>0.9613638813786134</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TotalArea</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-4.43105053568337</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4.549825367450647</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.04987527794819459</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.02928924690896462</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9982698396373867</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9965426727296537</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TotalBaths</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-1.541932106739068</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6.100118956929524</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.01982587280206892</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.2682569294609691</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.059486284817845</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.122511187717119</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TotalPorchArea</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-2.048330799186041</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1.452026218752154</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.03709956648153026</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.4186184458785633</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9640951297230876</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.9294794191557773</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AvgRoomSize</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-3.022724151827771</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4.790724894174276</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01400908740816321</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.01087748362587381</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.036268435441732</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.073852270292854</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LotUtilization</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-1.540516045667566</v>
+      </c>
+      <c r="C38" t="n">
+        <v>6.489817154385387</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.03714023029670504</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.2050902758165994</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.053086746785433</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.108991696255127</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Qual_x_Area</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-4.750423494734186</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.470307855474133</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.03927838764801456</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.02440765075326051</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.9823503552735821</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9650122205061329</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TotalQualCond</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-5.12399780496265</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.145604653263687</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.02482797428798452</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1921752038971382</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.022757239405399</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.046032370756152</v>
       </c>
     </row>
   </sheetData>

--- a/summary/test_data_after_stand_summary.xlsx
+++ b/summary/test_data_after_stand_summary.xlsx
@@ -455,22 +455,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.6628930854346</v>
+        <v>-1.655820968246297</v>
       </c>
       <c r="C2" t="n">
-        <v>4.108707781639016</v>
+        <v>2.700484234974974</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008280077210762586</v>
+        <v>-0.02171576528056751</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1551611876935887</v>
+        <v>0.1640828502046944</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9311339270908809</v>
+        <v>0.9666495495136231</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8670103901796861</v>
+        <v>0.9344113515748906</v>
       </c>
     </row>
     <row r="3">
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-3.51372275852201</v>
+        <v>-3.407096896238303</v>
       </c>
       <c r="C3" t="n">
-        <v>3.54378318206067</v>
+        <v>3.477516546028645</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06209065808206438</v>
+        <v>-0.01401313253865638</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07250432859245991</v>
+        <v>0.06206108791000982</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9705138559104469</v>
+        <v>0.8774864319546438</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9418971445141637</v>
+        <v>0.7699824382644918</v>
       </c>
     </row>
     <row r="4">
@@ -505,22 +505,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.8068408258386879</v>
+        <v>-0.814082116124212</v>
       </c>
       <c r="C4" t="n">
-        <v>1.919017976538475</v>
+        <v>1.693261944309747</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.03123400933166015</v>
+        <v>-0.06398646584442212</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8068408258386879</v>
+        <v>-0.814082116124212</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9944594830576402</v>
+        <v>0.9650335880387071</v>
       </c>
       <c r="G4" t="n">
-        <v>0.988949663443269</v>
+        <v>0.931289826042861</v>
       </c>
     </row>
     <row r="5">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1.4141397865663</v>
+        <v>-1.387610692907509</v>
       </c>
       <c r="C5" t="n">
-        <v>1.359755117188353</v>
+        <v>1.167362451449006</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.003194400053604423</v>
+        <v>0.08740995844074641</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5453160443695331</v>
+        <v>0.6232439307040534</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9938407378181153</v>
+        <v>0.9660810072405761</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9877194121468559</v>
+        <v>0.933312512550966</v>
       </c>
     </row>
     <row r="6">
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.3553424078009089</v>
+        <v>-0.3499719275005094</v>
       </c>
       <c r="C6" t="n">
-        <v>3.619397294573782</v>
+        <v>3.502305635704364</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02774242919187456</v>
+        <v>0.0479071322602761</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3553424078009089</v>
+        <v>-0.3499719275005094</v>
       </c>
       <c r="F6" t="n">
-        <v>1.03650473134005</v>
+        <v>1.05887192071251</v>
       </c>
       <c r="G6" t="n">
-        <v>1.074342058090309</v>
+        <v>1.121209744473401</v>
       </c>
     </row>
     <row r="7">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-3.047600483023416</v>
+        <v>-3.061597250143507</v>
       </c>
       <c r="C7" t="n">
-        <v>1.090248548991072</v>
+        <v>1.058938646882095</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02499996940429135</v>
+        <v>-0.04046456053768796</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2616942802953399</v>
+        <v>0.2202342558770444</v>
       </c>
       <c r="F7" t="n">
-        <v>1.017019427294358</v>
+        <v>1.010732190976473</v>
       </c>
       <c r="G7" t="n">
-        <v>1.034328515494143</v>
+        <v>1.021579561876101</v>
       </c>
     </row>
     <row r="8">
@@ -605,22 +605,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.894038092795351</v>
+        <v>-5.855128763550051</v>
       </c>
       <c r="C8" t="n">
-        <v>1.55908504243069</v>
+        <v>2775.204671696012</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.03445878275956157</v>
+        <v>904.327667239879</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1275926859917272</v>
+        <v>860.7321265886341</v>
       </c>
       <c r="F8" t="n">
-        <v>1.06363056586247</v>
+        <v>360.809525656545</v>
       </c>
       <c r="G8" t="n">
-        <v>1.131309980636918</v>
+        <v>130183.513804501</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-3.142498956705619</v>
+        <v>1145.739534166004</v>
       </c>
       <c r="C9" t="n">
-        <v>4.814531495952832</v>
+        <v>7398.794182297473</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.02689889296058504</v>
+        <v>3621.261758505956</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07480144481180019</v>
+        <v>3361.932597208583</v>
       </c>
       <c r="F9" t="n">
-        <v>1.033150066875349</v>
+        <v>1148.386026412282</v>
       </c>
       <c r="G9" t="n">
-        <v>1.067399060684537</v>
+        <v>1318790.465658992</v>
       </c>
     </row>
     <row r="10">
@@ -655,22 +655,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.8701173641387884</v>
+        <v>-0.8826071464803253</v>
       </c>
       <c r="C10" t="n">
-        <v>1.417101304379369</v>
+        <v>1.349842212616043</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.02127073533022548</v>
+        <v>-0.0753484435751294</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8701173641387884</v>
+        <v>-0.8826071464803253</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9906482208258371</v>
+        <v>0.9844648437125937</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9813838974253967</v>
+        <v>0.9691710285060614</v>
       </c>
     </row>
     <row r="11">
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.1336023189084742</v>
+        <v>-0.1308461190789479</v>
       </c>
       <c r="C11" t="n">
-        <v>9.196811486322643</v>
+        <v>8.363586621432294</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.06082564021632841</v>
+        <v>0.0249049246299193</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1336023189084742</v>
+        <v>-0.1308461190789479</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7457918627386499</v>
+        <v>1.082323870103862</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5562055025271853</v>
+        <v>1.171424959796602</v>
       </c>
     </row>
     <row r="12">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-3.773369383838025</v>
+        <v>-2.450546058954449</v>
       </c>
       <c r="C12" t="n">
-        <v>3.804747536638441</v>
+        <v>2.441834156033114</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.04208946648837993</v>
+        <v>-0.06541929832883106</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.002960281451987794</v>
+        <v>0.02204076276747855</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9481633607835332</v>
+        <v>0.9432803424952682</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8990137587323246</v>
+        <v>0.8897778045379905</v>
       </c>
     </row>
     <row r="13">
@@ -730,22 +730,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.8199643654586394</v>
+        <v>-0.7930957731111337</v>
       </c>
       <c r="C13" t="n">
-        <v>4.963359178355918</v>
+        <v>3.058612596925474</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01641758638842831</v>
+        <v>0.1302589731305188</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8199643654586394</v>
+        <v>-0.7930957731111337</v>
       </c>
       <c r="F13" t="n">
-        <v>1.02273680627082</v>
+        <v>0.9898612157890841</v>
       </c>
       <c r="G13" t="n">
-        <v>1.045990574901038</v>
+        <v>0.9798252265234438</v>
       </c>
     </row>
     <row r="14">
@@ -755,22 +755,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2429231735496986</v>
+        <v>-0.2531860696853492</v>
       </c>
       <c r="C14" t="n">
-        <v>6.515952899906281</v>
+        <v>3.844384066165255</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03231738131833545</v>
+        <v>-0.09882555086905938</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2429231735496986</v>
+        <v>-0.2531860696853492</v>
       </c>
       <c r="F14" t="n">
-        <v>1.059175396114358</v>
+        <v>0.781516187922797</v>
       </c>
       <c r="G14" t="n">
-        <v>1.121852519734007</v>
+        <v>0.6107675519853806</v>
       </c>
     </row>
     <row r="15">
@@ -780,22 +780,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-2.841822193737443</v>
+        <v>-2.830051435678058</v>
       </c>
       <c r="C15" t="n">
-        <v>4.42130323795913</v>
+        <v>2.562281479284375</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01065955565401416</v>
+        <v>-0.08463992874512968</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7897405221108432</v>
+        <v>0.7648371742968976</v>
       </c>
       <c r="F15" t="n">
-        <v>1.008103448803146</v>
+        <v>0.9470285714792001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.016272563488797</v>
+        <v>0.8968631151979344</v>
       </c>
     </row>
     <row r="16">
@@ -805,22 +805,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.7616206719986545</v>
+        <v>-0.7741510599881057</v>
       </c>
       <c r="C16" t="n">
-        <v>3.216791425024728</v>
+        <v>1.409089602818099</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.01038521433591149</v>
+        <v>-0.2894184286907563</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7616206719986545</v>
+        <v>-0.7741510599881057</v>
       </c>
       <c r="F16" t="n">
-        <v>1.000603816274454</v>
+        <v>0.672579136205681</v>
       </c>
       <c r="G16" t="n">
-        <v>1.001207997143001</v>
+        <v>0.4523626944591799</v>
       </c>
     </row>
     <row r="17">
@@ -830,22 +830,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-3.514951815977729</v>
+        <v>-3.514190702959939</v>
       </c>
       <c r="C17" t="n">
-        <v>3.842510049724758</v>
+        <v>3.819772503217325</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.01524068863192643</v>
+        <v>-0.05232565072900446</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1637791168735145</v>
+        <v>0.152790900128693</v>
       </c>
       <c r="F17" t="n">
-        <v>1.017522705904964</v>
+        <v>0.984500585939227</v>
       </c>
       <c r="G17" t="n">
-        <v>1.03535245703216</v>
+        <v>0.9692414037146811</v>
       </c>
     </row>
     <row r="18">
@@ -855,22 +855,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-7.975078122202384</v>
+        <v>-0.1973340773744095</v>
       </c>
       <c r="C18" t="n">
-        <v>4.336071900852138</v>
+        <v>7.843865217684576</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0189434437639029</v>
+        <v>0.08794674478318451</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2076072719753528</v>
+        <v>-0.1973340773744095</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9764078540158971</v>
+        <v>1.164934671215235</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9533722973839296</v>
+        <v>1.357072788199347</v>
       </c>
     </row>
     <row r="19">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-3.158172338244525</v>
+        <v>-3.164904110649903</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.304982300166768</v>
+        <v>-2.440761782137344</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.79308723637513</v>
+        <v>-2.797333954870547</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.813758749898229</v>
+        <v>-2.821087233781141</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1224726172068784</v>
+        <v>0.1282525563071167</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01499954196550256</v>
+        <v>0.01644871819931013</v>
       </c>
     </row>
     <row r="20">
@@ -905,22 +905,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.9512264882332893</v>
+        <v>-0.9757566742154179</v>
       </c>
       <c r="C20" t="n">
-        <v>1.546172798104521</v>
+        <v>1.218600574588249</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3635634864496854</v>
+        <v>-0.370941043674209</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9512264882332893</v>
+        <v>-0.9757566742154179</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6126876980697885</v>
+        <v>0.6531350197591029</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3753862153660563</v>
+        <v>0.4265853540357238</v>
       </c>
     </row>
     <row r="21">
@@ -930,22 +930,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.365439947036252</v>
+        <v>-2.355716144368795</v>
       </c>
       <c r="C21" t="n">
-        <v>4.327471531012058</v>
+        <v>2.930501831851672</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.002966053139829951</v>
+        <v>-0.1018321099871236</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3117246441830721</v>
+        <v>0.2873928437414381</v>
       </c>
       <c r="F21" t="n">
-        <v>1.040153105934515</v>
+        <v>0.9318149471610981</v>
       </c>
       <c r="G21" t="n">
-        <v>1.081918483785219</v>
+        <v>0.8682790957528401</v>
       </c>
     </row>
     <row r="22">
@@ -955,22 +955,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-2.212962983088507</v>
+        <v>-2.199502349712417</v>
       </c>
       <c r="C22" t="n">
-        <v>4.749039564876986</v>
+        <v>4.210075491535244</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.002504598025378754</v>
+        <v>-0.0924649666279822</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03284429044874903</v>
+        <v>0.01387704870404144</v>
       </c>
       <c r="F22" t="n">
-        <v>1.016821536426008</v>
+        <v>0.9234338104631777</v>
       </c>
       <c r="G22" t="n">
-        <v>1.033926036939747</v>
+        <v>0.8527300023065442</v>
       </c>
     </row>
     <row r="23">
@@ -980,22 +980,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.9467014684878265</v>
+        <v>-0.9396395438469278</v>
       </c>
       <c r="C23" t="n">
-        <v>1.851141160926364</v>
+        <v>1.569469841943983</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.005813519417281798</v>
+        <v>0.04020105647549305</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9467014684878265</v>
+        <v>-0.9396395438469278</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9975144226316524</v>
+        <v>1.006237340585405</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9950350233581589</v>
+        <v>1.012513585588388</v>
       </c>
     </row>
     <row r="24">
@@ -1005,22 +1005,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-1.072916474962699</v>
+        <v>-1.095131419551467</v>
       </c>
       <c r="C24" t="n">
-        <v>1.999467862252639</v>
+        <v>1.817270790936693</v>
       </c>
       <c r="D24" t="n">
-        <v>0.02274895877874982</v>
+        <v>-0.1068090945947288</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4920665308869768</v>
+        <v>0.160289954227759</v>
       </c>
       <c r="F24" t="n">
-        <v>1.002277710386582</v>
+        <v>1.001129601005861</v>
       </c>
       <c r="G24" t="n">
-        <v>1.004560608737769</v>
+        <v>1.002260478010154</v>
       </c>
     </row>
     <row r="25">
@@ -1030,22 +1030,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4042442108783149</v>
+        <v>-0.4021861793845504</v>
       </c>
       <c r="C25" t="n">
-        <v>3.603730653062192</v>
+        <v>2.938919864502066</v>
       </c>
       <c r="D25" t="n">
-        <v>0.068843772296505</v>
+        <v>0.01168591208856506</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4042442108783149</v>
+        <v>-0.4021861793845504</v>
       </c>
       <c r="F25" t="n">
-        <v>1.050573391074073</v>
+        <v>1.005116126166419</v>
       </c>
       <c r="G25" t="n">
-        <v>1.103704450032877</v>
+        <v>1.010258427079789</v>
       </c>
     </row>
     <row r="26">
@@ -1055,22 +1055,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1285214274886148</v>
+        <v>-0.127701024055796</v>
       </c>
       <c r="C26" t="n">
-        <v>8.705045196618768</v>
+        <v>8.593376676621247</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.05846576540103778</v>
+        <v>0.008828102037813122</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1285214274886148</v>
+        <v>-0.127701024055796</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7410126719471999</v>
+        <v>1.037999735470898</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5490997799863285</v>
+        <v>1.077443450837653</v>
       </c>
     </row>
     <row r="27">
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2927694190084836</v>
+        <v>-0.2878825621456251</v>
       </c>
       <c r="C27" t="n">
-        <v>4.239762916060005</v>
+        <v>4.037401318198151</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05782549382688938</v>
+        <v>0.04478644579162489</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2927694190084836</v>
+        <v>-0.2878825621456251</v>
       </c>
       <c r="F27" t="n">
-        <v>1.079150320875313</v>
+        <v>1.06878709679007</v>
       </c>
       <c r="G27" t="n">
-        <v>1.16456541504529</v>
+        <v>1.142305858264946</v>
       </c>
     </row>
     <row r="28">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.06939258050999438</v>
+        <v>-0.07763000441188135</v>
       </c>
       <c r="C28" t="n">
-        <v>15.17652734628317</v>
+        <v>-0.07763000441188135</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.01400732729409562</v>
+        <v>-0.07763000441188136</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.06939258050999438</v>
+        <v>-0.07763000441188135</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8661314924819761</v>
+        <v>1.390161235377871e-17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7501837622690554</v>
+        <v>1.932548260347329e-34</v>
       </c>
     </row>
     <row r="29">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1904814736846831</v>
+        <v>-0.1664233792932206</v>
       </c>
       <c r="C29" t="n">
-        <v>7.757422084593538</v>
+        <v>7.282179750836266</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002139563366975658</v>
+        <v>0.2332932218487416</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1904814736846831</v>
+        <v>-0.1664233792932206</v>
       </c>
       <c r="F29" t="n">
-        <v>1.02369480634146</v>
+        <v>1.490285210673869</v>
       </c>
       <c r="G29" t="n">
-        <v>1.04795105653048</v>
+        <v>2.220950009153259</v>
       </c>
     </row>
     <row r="30">
@@ -1155,22 +1155,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.208604423534465</v>
+        <v>-1.179920945287459</v>
       </c>
       <c r="C30" t="n">
-        <v>3.0572980713771</v>
+        <v>3.287171533593825</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.004475355920606944</v>
+        <v>0.14717494563539</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.08425802952676548</v>
+        <v>0.1105724375004672</v>
       </c>
       <c r="F30" t="n">
-        <v>1.00633683853893</v>
+        <v>0.9961374501857186</v>
       </c>
       <c r="G30" t="n">
-        <v>1.012713832600527</v>
+        <v>0.9922898196625051</v>
       </c>
     </row>
     <row r="31">
@@ -1180,22 +1180,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.112339552660391</v>
+        <v>-1.085456172774963</v>
       </c>
       <c r="C31" t="n">
-        <v>1.795650921645751</v>
+        <v>1.825932704600626</v>
       </c>
       <c r="D31" t="n">
-        <v>0.05613845663500069</v>
+        <v>0.140916539270234</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3368754261787526</v>
+        <v>-0.1635163616060263</v>
       </c>
       <c r="F31" t="n">
-        <v>1.024070844269315</v>
+        <v>0.9996145763174065</v>
       </c>
       <c r="G31" t="n">
-        <v>1.048721094082468</v>
+        <v>0.9992293011862281</v>
       </c>
     </row>
     <row r="32">
@@ -1205,22 +1205,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.109798062474761</v>
+        <v>-1.080042826903726</v>
       </c>
       <c r="C32" t="n">
-        <v>3.460879430369108</v>
+        <v>2.879737513643902</v>
       </c>
       <c r="D32" t="n">
-        <v>0.03599031735836826</v>
+        <v>0.1355061817450788</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0673628448086158</v>
+        <v>0.159888390843511</v>
       </c>
       <c r="F32" t="n">
-        <v>1.040700231950271</v>
+        <v>0.9822060202013329</v>
       </c>
       <c r="G32" t="n">
-        <v>1.083056972781347</v>
+        <v>0.9647286661197412</v>
       </c>
     </row>
     <row r="33">
@@ -1230,22 +1230,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.367654733107055</v>
+        <v>1.52066588410237</v>
       </c>
       <c r="C33" t="n">
-        <v>1.645209711006642</v>
+        <v>2.453511342417312</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.03468420625620441</v>
+        <v>2.079734223845914</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1387774889497933</v>
+        <v>2.453511342417312</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9804916528857415</v>
+        <v>0.4579138047810678</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9613638813786134</v>
+        <v>0.2096850526090739</v>
       </c>
     </row>
     <row r="34">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-4.43105053568337</v>
+        <v>2577.726243680593</v>
       </c>
       <c r="C34" t="n">
-        <v>4.549825367450647</v>
+        <v>16561.52235568919</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.04987527794819459</v>
+        <v>7936.729498117495</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.02928924690896462</v>
+        <v>7650.156336515394</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9982698396373867</v>
+        <v>2309.821104909081</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9965426727296537</v>
+        <v>5335273.536683406</v>
       </c>
     </row>
     <row r="35">
@@ -1280,22 +1280,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.541932106739068</v>
+        <v>-1.533653561228353</v>
       </c>
       <c r="C35" t="n">
-        <v>6.100118956929524</v>
+        <v>2.894012934747286</v>
       </c>
       <c r="D35" t="n">
-        <v>0.01982587280206892</v>
+        <v>-0.01083088673183891</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.2682569294609691</v>
+        <v>-0.2686059909495987</v>
       </c>
       <c r="F35" t="n">
-        <v>1.059486284817845</v>
+        <v>0.9672651134104102</v>
       </c>
       <c r="G35" t="n">
-        <v>1.122511187717119</v>
+        <v>0.9356017996208538</v>
       </c>
     </row>
     <row r="36">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-2.048330799186041</v>
+        <v>-2.031704909597648</v>
       </c>
       <c r="C36" t="n">
-        <v>1.452026218752154</v>
+        <v>1.143020168476235</v>
       </c>
       <c r="D36" t="n">
-        <v>0.03709956648153026</v>
+        <v>0.03097776491400492</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4186184458785633</v>
+        <v>0.4226823454675091</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9640951297230876</v>
+        <v>0.9755511490258755</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9294794191557773</v>
+        <v>0.951700044365706</v>
       </c>
     </row>
     <row r="37">
@@ -1330,22 +1330,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-3.022724151827771</v>
+        <v>-2.492026631465373</v>
       </c>
       <c r="C37" t="n">
-        <v>4.790724894174276</v>
+        <v>3.327456733695477</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01400908740816321</v>
+        <v>-0.04316565068573863</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.01087748362587381</v>
+        <v>-0.08344436065391789</v>
       </c>
       <c r="F37" t="n">
-        <v>1.036268435441732</v>
+        <v>0.9877304320079771</v>
       </c>
       <c r="G37" t="n">
-        <v>1.073852270292854</v>
+        <v>0.975611406314665</v>
       </c>
     </row>
     <row r="38">
@@ -1355,22 +1355,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.540516045667566</v>
+        <v>-1.54566434449761</v>
       </c>
       <c r="C38" t="n">
-        <v>6.489817154385387</v>
+        <v>4.530985493134529</v>
       </c>
       <c r="D38" t="n">
-        <v>0.03714023029670504</v>
+        <v>-0.05022489616252219</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.2050902758165994</v>
+        <v>-0.1830563788577478</v>
       </c>
       <c r="F38" t="n">
-        <v>1.053086746785433</v>
+        <v>0.9092301340675555</v>
       </c>
       <c r="G38" t="n">
-        <v>1.108991696255127</v>
+        <v>0.8266994366965049</v>
       </c>
     </row>
     <row r="39">
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4.750423494734186</v>
+        <v>-2.338900165889119</v>
       </c>
       <c r="C39" t="n">
-        <v>3.470307855474133</v>
+        <v>2.135849191792333</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.03927838764801456</v>
+        <v>-0.07681430322222983</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.02440765075326051</v>
+        <v>-0.0115406535105819</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9823503552735821</v>
+        <v>0.9233456733186703</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9650122205061329</v>
+        <v>0.8525672324363087</v>
       </c>
     </row>
     <row r="40">
@@ -1405,22 +1405,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.12399780496265</v>
+        <v>-3.979021525585972</v>
       </c>
       <c r="C40" t="n">
-        <v>3.145604653263687</v>
+        <v>3.15816374477658</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.02482797428798452</v>
+        <v>-0.04582952870523894</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1921752038971382</v>
+        <v>0.1843365487921836</v>
       </c>
       <c r="F40" t="n">
-        <v>1.022757239405399</v>
+        <v>1.035032193175979</v>
       </c>
       <c r="G40" t="n">
-        <v>1.046032370756152</v>
+        <v>1.071291640910677</v>
       </c>
     </row>
   </sheetData>

--- a/summary/test_data_after_stand_summary.xlsx
+++ b/summary/test_data_after_stand_summary.xlsx
@@ -608,19 +608,19 @@
         <v>-5.855128763550051</v>
       </c>
       <c r="C8" t="n">
-        <v>2775.204671696012</v>
+        <v>1.147912222385847</v>
       </c>
       <c r="D8" t="n">
-        <v>904.327667239879</v>
+        <v>0.003380968951634878</v>
       </c>
       <c r="E8" t="n">
-        <v>860.7321265886341</v>
+        <v>0.1370321855965894</v>
       </c>
       <c r="F8" t="n">
-        <v>360.809525656545</v>
+        <v>0.9687868586439029</v>
       </c>
       <c r="G8" t="n">
-        <v>130183.513804501</v>
+        <v>0.9385479774811215</v>
       </c>
     </row>
     <row r="9">
@@ -630,22 +630,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1145.739534166004</v>
+        <v>-3.411256819778386</v>
       </c>
       <c r="C9" t="n">
-        <v>7398.794182297473</v>
+        <v>2.386489066411812</v>
       </c>
       <c r="D9" t="n">
-        <v>3621.261758505956</v>
+        <v>0.002659135564025452</v>
       </c>
       <c r="E9" t="n">
-        <v>3361.932597208583</v>
+        <v>-0.07688591485743884</v>
       </c>
       <c r="F9" t="n">
-        <v>1148.386026412282</v>
+        <v>0.9820329559745874</v>
       </c>
       <c r="G9" t="n">
-        <v>1318790.465658992</v>
+        <v>0.9643887266201859</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         <v>-0.7741510599881057</v>
       </c>
       <c r="C16" t="n">
-        <v>1.409089602818099</v>
+        <v>3.200391524917861</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2894184286907563</v>
+        <v>-0.06635580514183767</v>
       </c>
       <c r="E16" t="n">
         <v>-0.7741510599881057</v>
       </c>
       <c r="F16" t="n">
-        <v>0.672579136205681</v>
+        <v>0.9950612528871853</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4523626944591799</v>
+        <v>0.9901468969974149</v>
       </c>
     </row>
     <row r="17">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-3.164904110649903</v>
+        <v>-2.173475268028877</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.440761782137344</v>
+        <v>3.355946807847104</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.797333954870547</v>
+        <v>-0.06101721468812907</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.821087233781141</v>
+        <v>-0.3303345760702164</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1282525563071167</v>
+        <v>0.9915027984213365</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01644871819931013</v>
+        <v>0.9830777992773415</v>
       </c>
     </row>
     <row r="20">
@@ -908,19 +908,19 @@
         <v>-0.9757566742154179</v>
       </c>
       <c r="C20" t="n">
-        <v>1.218600574588249</v>
+        <v>3.772925806966282</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.370941043674209</v>
+        <v>-0.02710435206153943</v>
       </c>
       <c r="E20" t="n">
         <v>-0.9757566742154179</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6531350197591029</v>
+        <v>1.098386621360821</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4265853540357238</v>
+        <v>1.206453169984439</v>
       </c>
     </row>
     <row r="21">
@@ -1255,22 +1255,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2577.726243680593</v>
+        <v>-3.42633836402491</v>
       </c>
       <c r="C34" t="n">
-        <v>16561.52235568919</v>
+        <v>2.398623617695005</v>
       </c>
       <c r="D34" t="n">
-        <v>7936.729498117495</v>
+        <v>-0.04194533487897204</v>
       </c>
       <c r="E34" t="n">
-        <v>7650.156336515394</v>
+        <v>-0.0256093963221754</v>
       </c>
       <c r="F34" t="n">
-        <v>2309.821104909081</v>
+        <v>0.9226646726798688</v>
       </c>
       <c r="G34" t="n">
-        <v>5335273.536683406</v>
+        <v>0.8513100982114495</v>
       </c>
     </row>
     <row r="35">
